--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.01497457974129516</v>
       </c>
       <c r="C2" t="n">
-        <v>18638316</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18638316</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>14151286</v>
+        <v>4521822</v>
       </c>
       <c r="L2" t="n">
-        <v>8828620</v>
+        <v>2692872</v>
       </c>
       <c r="M2" t="n">
-        <v>2420274</v>
+        <v>704771</v>
       </c>
       <c r="N2" t="n">
-        <v>163058</v>
+        <v>40242</v>
       </c>
       <c r="O2" t="n">
-        <v>1385467</v>
+        <v>418682</v>
       </c>
       <c r="P2" t="n">
-        <v>541851</v>
+        <v>168826</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999983549118042</v>
+        <v>0.9999625086784363</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9581775069236755</v>
+        <v>0.9184937477111816</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9121877551078796</v>
+        <v>0.8346494436264038</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8636087775230408</v>
+        <v>0.7545534372329712</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7522444128990173</v>
+        <v>0.5592273473739624</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9080462455749512</v>
+        <v>0.8233100771903992</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9341244101524353</v>
+        <v>0.8727518916130066</v>
       </c>
       <c r="X2" t="n">
-        <v>18638316</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18638316</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>13630633</v>
+        <v>4372711</v>
       </c>
       <c r="AG2" t="n">
-        <v>8082091</v>
+        <v>2479581</v>
       </c>
       <c r="AH2" t="n">
-        <v>2133126</v>
+        <v>632335</v>
       </c>
       <c r="AI2" t="n">
-        <v>140214</v>
+        <v>36469</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1261051</v>
+        <v>384092</v>
       </c>
       <c r="AK2" t="n">
-        <v>507400</v>
+        <v>158512</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9201671481132507</v>
+        <v>0.88556969165802</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8408105969429016</v>
+        <v>0.773880660533905</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7677744030952454</v>
+        <v>0.6827875375747681</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.528842031955719</v>
+        <v>0.412647932767868</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8273733258247375</v>
+        <v>0.7560062408447266</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8751459717750549</v>
+        <v>0.820188045501709</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.003701645093703551</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>14151286</v>
+        <v>4521822</v>
       </c>
       <c r="E3" t="n">
-        <v>586120</v>
+        <v>372910</v>
       </c>
       <c r="F3" t="n">
-        <v>28437</v>
+        <v>17962</v>
       </c>
       <c r="G3" t="n">
-        <v>6398</v>
+        <v>3905</v>
       </c>
       <c r="H3" t="n">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="I3" t="n">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="J3" t="n">
-        <v>29572577</v>
+        <v>9857395</v>
       </c>
       <c r="K3" t="n">
-        <v>32820880</v>
+        <v>10752235</v>
       </c>
       <c r="L3" t="n">
-        <v>37717098</v>
+        <v>12316232</v>
       </c>
       <c r="M3" t="n">
-        <v>45044460</v>
+        <v>14912013</v>
       </c>
       <c r="N3" t="n">
-        <v>47891859</v>
+        <v>15950065</v>
       </c>
       <c r="O3" t="n">
-        <v>46544856</v>
+        <v>15471563</v>
       </c>
       <c r="P3" t="n">
-        <v>47593142</v>
+        <v>15852484</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.957938551902771</v>
+        <v>0.9196484088897705</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9154321551322937</v>
+        <v>0.8361167311668396</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8691945672035217</v>
+        <v>0.7585245966911316</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6138376593589783</v>
+        <v>0.4541115164756775</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9078814387321472</v>
+        <v>0.822583794593811</v>
       </c>
       <c r="W3" t="n">
-        <v>0.934473991394043</v>
+        <v>0.8733839988708496</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>13630633</v>
+        <v>4372711</v>
       </c>
       <c r="Z3" t="n">
-        <v>1067083</v>
+        <v>509446</v>
       </c>
       <c r="AA3" t="n">
-        <v>44908</v>
+        <v>21836</v>
       </c>
       <c r="AB3" t="n">
-        <v>29408</v>
+        <v>12498</v>
       </c>
       <c r="AC3" t="n">
-        <v>463</v>
+        <v>346</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="AE3" t="n">
-        <v>29572884</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>32255974</v>
+        <v>10588470</v>
       </c>
       <c r="AG3" t="n">
-        <v>37036820</v>
+        <v>12125205</v>
       </c>
       <c r="AH3" t="n">
-        <v>44781500</v>
+        <v>14847493</v>
       </c>
       <c r="AI3" t="n">
-        <v>47820643</v>
+        <v>15929874</v>
       </c>
       <c r="AJ3" t="n">
-        <v>46422045</v>
+        <v>15437454</v>
       </c>
       <c r="AK3" t="n">
-        <v>47558965</v>
+        <v>15842348</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9226941466331482</v>
+        <v>0.8893222212791443</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8380252122879028</v>
+        <v>0.7698915004730225</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7660709023475647</v>
+        <v>0.6805638074874878</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5278406143188477</v>
+        <v>0.4115350246429443</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.8263529539108276</v>
+        <v>0.7546249032020569</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8750599026679993</v>
+        <v>0.8200268149375916</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0454970835507619</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>581674</v>
+        <v>379561</v>
       </c>
       <c r="E4" t="n">
-        <v>8828620</v>
+        <v>2692872</v>
       </c>
       <c r="F4" t="n">
-        <v>219315</v>
+        <v>137261</v>
       </c>
       <c r="G4" t="n">
-        <v>6919</v>
+        <v>4548</v>
       </c>
       <c r="H4" t="n">
-        <v>7134</v>
+        <v>5993</v>
       </c>
       <c r="I4" t="n">
-        <v>523</v>
+        <v>431</v>
       </c>
       <c r="J4" t="n">
-        <v>307</v>
+        <v>233</v>
       </c>
       <c r="K4" t="n">
-        <v>617675</v>
+        <v>401262</v>
       </c>
       <c r="L4" t="n">
-        <v>849892</v>
+        <v>533479</v>
       </c>
       <c r="M4" t="n">
-        <v>382238</v>
+        <v>229253</v>
       </c>
       <c r="N4" t="n">
-        <v>53704</v>
+        <v>31718</v>
       </c>
       <c r="O4" t="n">
-        <v>140300</v>
+        <v>89853</v>
       </c>
       <c r="P4" t="n">
-        <v>38212</v>
+        <v>24615</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999991774559021</v>
+        <v>0.9999812245368958</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9580580592155457</v>
+        <v>0.9190707206726074</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9138070940971375</v>
+        <v>0.8353824615478516</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8663926124572754</v>
+        <v>0.7565338611602783</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6760296225547791</v>
+        <v>0.5012175440788269</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9079638123512268</v>
+        <v>0.8229467868804932</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9342991709709167</v>
+        <v>0.8730678558349609</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1118520</v>
+        <v>536843</v>
       </c>
       <c r="Z4" t="n">
-        <v>8082091</v>
+        <v>2479581</v>
       </c>
       <c r="AA4" t="n">
-        <v>395945</v>
+        <v>178536</v>
       </c>
       <c r="AB4" t="n">
-        <v>26051</v>
+        <v>11674</v>
       </c>
       <c r="AC4" t="n">
-        <v>20011</v>
+        <v>12933</v>
       </c>
       <c r="AD4" t="n">
-        <v>1592</v>
+        <v>1122</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1182581</v>
+        <v>565027</v>
       </c>
       <c r="AG4" t="n">
-        <v>1530170</v>
+        <v>724506</v>
       </c>
       <c r="AH4" t="n">
-        <v>645198</v>
+        <v>293773</v>
       </c>
       <c r="AI4" t="n">
-        <v>124920</v>
+        <v>51909</v>
       </c>
       <c r="AJ4" t="n">
-        <v>263111</v>
+        <v>123962</v>
       </c>
       <c r="AK4" t="n">
-        <v>72389</v>
+        <v>34751</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.921428918838501</v>
+        <v>0.8874420523643494</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.8394155502319336</v>
+        <v>0.7718809247016907</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.7669216990470886</v>
+        <v>0.6816738843917847</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5283408761024475</v>
+        <v>0.4120906889438629</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8268628120422363</v>
+        <v>0.7553150057792664</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8751029372215271</v>
+        <v>0.8201074004173279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>20259</v>
+        <v>12296</v>
       </c>
       <c r="E5" t="n">
-        <v>237951</v>
+        <v>145041</v>
       </c>
       <c r="F5" t="n">
-        <v>2420274</v>
+        <v>704771</v>
       </c>
       <c r="G5" t="n">
-        <v>21939</v>
+        <v>12705</v>
       </c>
       <c r="H5" t="n">
-        <v>80894</v>
+        <v>51805</v>
       </c>
       <c r="I5" t="n">
-        <v>3149</v>
+        <v>2482</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>621359</v>
+        <v>395081</v>
       </c>
       <c r="L5" t="n">
-        <v>815590</v>
+        <v>527817</v>
       </c>
       <c r="M5" t="n">
-        <v>364228</v>
+        <v>224363</v>
       </c>
       <c r="N5" t="n">
-        <v>102579</v>
+        <v>48375</v>
       </c>
       <c r="O5" t="n">
-        <v>140577</v>
+        <v>90302</v>
       </c>
       <c r="P5" t="n">
-        <v>37995</v>
+        <v>24475</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999993622303009</v>
+        <v>0.9999855160713196</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9742998480796814</v>
+        <v>0.950446605682373</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9654544591903687</v>
+        <v>0.9339596033096313</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9845167398452759</v>
+        <v>0.9717732071876526</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9967583417892456</v>
+        <v>0.9950160980224609</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9941740036010742</v>
+        <v>0.9887896180152893</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9984192848205566</v>
+        <v>0.996945321559906</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>36860</v>
+        <v>16840</v>
       </c>
       <c r="Z5" t="n">
-        <v>417337</v>
+        <v>189907</v>
       </c>
       <c r="AA5" t="n">
-        <v>2133126</v>
+        <v>632335</v>
       </c>
       <c r="AB5" t="n">
-        <v>38924</v>
+        <v>15586</v>
       </c>
       <c r="AC5" t="n">
-        <v>149929</v>
+        <v>69220</v>
       </c>
       <c r="AD5" t="n">
-        <v>8326</v>
+        <v>5246</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1142012</v>
+        <v>544192</v>
       </c>
       <c r="AG5" t="n">
-        <v>1562119</v>
+        <v>741108</v>
       </c>
       <c r="AH5" t="n">
-        <v>651376</v>
+        <v>296799</v>
       </c>
       <c r="AI5" t="n">
-        <v>125423</v>
+        <v>52148</v>
       </c>
       <c r="AJ5" t="n">
-        <v>264993</v>
+        <v>124892</v>
       </c>
       <c r="AK5" t="n">
-        <v>72446</v>
+        <v>34789</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9517831206321716</v>
+        <v>0.9309775233268738</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9358595013618469</v>
+        <v>0.9088004231452942</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9731063842773438</v>
+        <v>0.9632509350776672</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9948073625564575</v>
+        <v>0.9935249090194702</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.989046037197113</v>
+        <v>0.9845147728919983</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9969958066940308</v>
+        <v>0.9956727623939514</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>15674</v>
+        <v>9364</v>
       </c>
       <c r="E6" t="n">
-        <v>19418</v>
+        <v>10041</v>
       </c>
       <c r="F6" t="n">
-        <v>49023</v>
+        <v>18506</v>
       </c>
       <c r="G6" t="n">
-        <v>163058</v>
+        <v>40242</v>
       </c>
       <c r="H6" t="n">
-        <v>16777</v>
+        <v>9405</v>
       </c>
       <c r="I6" t="n">
-        <v>1576</v>
+        <v>972</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>27010</v>
+        <v>11247</v>
       </c>
       <c r="Z6" t="n">
-        <v>26208</v>
+        <v>11948</v>
       </c>
       <c r="AA6" t="n">
-        <v>42660</v>
+        <v>17047</v>
       </c>
       <c r="AB6" t="n">
-        <v>140214</v>
+        <v>36469</v>
       </c>
       <c r="AC6" t="n">
-        <v>26865</v>
+        <v>10586</v>
       </c>
       <c r="AD6" t="n">
-        <v>2680</v>
+        <v>1320</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>6054</v>
+        <v>5231</v>
       </c>
       <c r="F7" t="n">
-        <v>83924</v>
+        <v>54314</v>
       </c>
       <c r="G7" t="n">
-        <v>17708</v>
+        <v>10079</v>
       </c>
       <c r="H7" t="n">
-        <v>1385467</v>
+        <v>418682</v>
       </c>
       <c r="I7" t="n">
-        <v>32828</v>
+        <v>20638</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Z7" t="n">
-        <v>18646</v>
+        <v>12624</v>
       </c>
       <c r="AA7" t="n">
-        <v>157635</v>
+        <v>73845</v>
       </c>
       <c r="AB7" t="n">
-        <v>29003</v>
+        <v>11380</v>
       </c>
       <c r="AC7" t="n">
-        <v>1261051</v>
+        <v>384092</v>
       </c>
       <c r="AD7" t="n">
-        <v>59641</v>
+        <v>26997</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="F8" t="n">
-        <v>1539</v>
+        <v>1210</v>
       </c>
       <c r="G8" t="n">
-        <v>740</v>
+        <v>481</v>
       </c>
       <c r="H8" t="n">
-        <v>35271</v>
+        <v>22478</v>
       </c>
       <c r="I8" t="n">
-        <v>541851</v>
+        <v>168826</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="Z8" t="n">
-        <v>896</v>
+        <v>581</v>
       </c>
       <c r="AA8" t="n">
-        <v>4050</v>
+        <v>2509</v>
       </c>
       <c r="AB8" t="n">
-        <v>1534</v>
+        <v>771</v>
       </c>
       <c r="AC8" t="n">
-        <v>65843</v>
+        <v>30877</v>
       </c>
       <c r="AD8" t="n">
-        <v>507400</v>
+        <v>158512</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
